--- a/artfynd/A 21283-2025 artfynd.xlsx
+++ b/artfynd/A 21283-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8058,6 +8058,112 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>127823971</v>
+      </c>
+      <c r="B65" t="n">
+        <v>58154</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>102993</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Svart rödstjärt</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Phoenicurus ochruros</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(S.G. Gmelin, 1774)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>södra bäcken, Beten, Storsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>406429</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6969654</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kent Moén</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kent Moén</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21283-2025 artfynd.xlsx
+++ b/artfynd/A 21283-2025 artfynd.xlsx
@@ -8063,7 +8063,7 @@
         <v>127823971</v>
       </c>
       <c r="B65" t="n">
-        <v>58154</v>
+        <v>58157</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 21283-2025 artfynd.xlsx
+++ b/artfynd/A 21283-2025 artfynd.xlsx
@@ -8063,7 +8063,7 @@
         <v>127823971</v>
       </c>
       <c r="B65" t="n">
-        <v>58157</v>
+        <v>58163</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 21283-2025 artfynd.xlsx
+++ b/artfynd/A 21283-2025 artfynd.xlsx
@@ -8063,7 +8063,7 @@
         <v>127823971</v>
       </c>
       <c r="B65" t="n">
-        <v>58163</v>
+        <v>58164</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 21283-2025 artfynd.xlsx
+++ b/artfynd/A 21283-2025 artfynd.xlsx
@@ -8063,7 +8063,7 @@
         <v>127823971</v>
       </c>
       <c r="B65" t="n">
-        <v>58164</v>
+        <v>58176</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 21283-2025 artfynd.xlsx
+++ b/artfynd/A 21283-2025 artfynd.xlsx
@@ -8063,7 +8063,7 @@
         <v>127823971</v>
       </c>
       <c r="B65" t="n">
-        <v>58176</v>
+        <v>58356</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 21283-2025 artfynd.xlsx
+++ b/artfynd/A 21283-2025 artfynd.xlsx
@@ -8063,7 +8063,7 @@
         <v>127823971</v>
       </c>
       <c r="B65" t="n">
-        <v>58356</v>
+        <v>58357</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>

--- a/artfynd/A 21283-2025 artfynd.xlsx
+++ b/artfynd/A 21283-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY66"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78598364</v>
+        <v>79105361</v>
       </c>
       <c r="B2" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ö om Åbergstjärnen, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406781.9749069838</v>
+        <v>406912</v>
       </c>
       <c r="R2" t="n">
-        <v>6969869.009862504</v>
+        <v>6969668</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,73 +754,72 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78598445</v>
+        <v>79104090</v>
       </c>
       <c r="B3" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ö om Åbergstjärnen, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406771.9802608408</v>
+        <v>406589</v>
       </c>
       <c r="R3" t="n">
-        <v>6969791.147681667</v>
+        <v>6969943</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,22 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,73 +860,72 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Låga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78598369</v>
+        <v>79105430</v>
       </c>
       <c r="B4" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ö om Åbergstjärnen, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406781.9749069838</v>
+        <v>406600</v>
       </c>
       <c r="R4" t="n">
-        <v>6969869.009862504</v>
+        <v>6969746</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,22 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,72 +966,67 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78598350</v>
+        <v>79105432</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ö om Åbergstjärnen, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406781.9749069838</v>
+        <v>406573</v>
       </c>
       <c r="R5" t="n">
-        <v>6969869.009862504</v>
+        <v>6969736</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,22 +1053,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,49 +1074,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79104074</v>
+        <v>79105449</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406743.0166012296</v>
+        <v>406533</v>
       </c>
       <c r="R6" t="n">
-        <v>6969866.91927859</v>
+        <v>6969746</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,19 +1158,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,15 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79105363</v>
+        <v>79105409</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,21 +1202,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406634.1506060475</v>
+        <v>406634</v>
       </c>
       <c r="R7" t="n">
-        <v>6969643.799806148</v>
+        <v>6969770</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,19 +1259,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,15 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79105420</v>
+        <v>79105425</v>
       </c>
       <c r="B8" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1413,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406696.6256436783</v>
+        <v>406650</v>
       </c>
       <c r="R8" t="n">
-        <v>6969764.500795629</v>
+        <v>6969781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,19 +1360,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,12 +1396,7 @@
         <v>79105459</v>
       </c>
       <c r="B9" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406560.1095949548</v>
+        <v>406560</v>
       </c>
       <c r="R9" t="n">
-        <v>6969759.706940949</v>
+        <v>6969760</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,19 +1461,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,15 +1494,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>79105443</v>
+        <v>79105451</v>
       </c>
       <c r="B10" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1621,21 +1505,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1645,10 +1529,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406638.250531808</v>
+        <v>406633</v>
       </c>
       <c r="R10" t="n">
-        <v>6969980.492526527</v>
+        <v>6969975</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,19 +1562,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,15 +1595,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>79104085</v>
+        <v>79105457</v>
       </c>
       <c r="B11" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,21 +1606,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>6439</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1761,10 +1630,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406716.0346333702</v>
+        <v>406614</v>
       </c>
       <c r="R11" t="n">
-        <v>6969980.105365257</v>
+        <v>6969783</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,19 +1663,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,15 +1696,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>79105361</v>
+        <v>79105360</v>
       </c>
       <c r="B12" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,21 +1707,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1877,10 +1731,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406912.179259451</v>
+        <v>406769</v>
       </c>
       <c r="R12" t="n">
-        <v>6969667.882959592</v>
+        <v>6969653</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,19 +1764,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,15 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>79105360</v>
+        <v>79105454</v>
       </c>
       <c r="B13" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1998,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406768.9719749739</v>
+        <v>406893</v>
       </c>
       <c r="R13" t="n">
-        <v>6969653.21563552</v>
+        <v>6969749</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,34 +1870,20 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2079,15 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>79105431</v>
+        <v>79105362</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2095,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2119,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406564.150269131</v>
+        <v>406651</v>
       </c>
       <c r="R14" t="n">
-        <v>6969724.858902014</v>
+        <v>6969983</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,19 +1972,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,15 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>79105364</v>
+        <v>79105363</v>
       </c>
       <c r="B15" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2235,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406616.0963194038</v>
+        <v>406634</v>
       </c>
       <c r="R15" t="n">
-        <v>6969957.81782157</v>
+        <v>6969644</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2268,19 +2073,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2311,15 +2106,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>79105460</v>
+        <v>79105364</v>
       </c>
       <c r="B16" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,21 +2117,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2351,10 +2141,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406491.6900784611</v>
+        <v>406616</v>
       </c>
       <c r="R16" t="n">
-        <v>6969896.016232851</v>
+        <v>6969958</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2384,19 +2174,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2427,37 +2207,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>79105457</v>
+        <v>79105412</v>
       </c>
       <c r="B17" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6439</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2467,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406613.8695416366</v>
+        <v>406695</v>
       </c>
       <c r="R17" t="n">
-        <v>6969783.310028824</v>
+        <v>6969616</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2500,19 +2275,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2543,15 +2308,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>79105450</v>
+        <v>79105413</v>
       </c>
       <c r="B18" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2559,21 +2319,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2583,10 +2343,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406711.4774721202</v>
+        <v>406698</v>
       </c>
       <c r="R18" t="n">
-        <v>6969964.697844785</v>
+        <v>6969632</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2616,19 +2376,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2659,37 +2409,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>79105416</v>
+        <v>79105441</v>
       </c>
       <c r="B19" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2699,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406686.4987209993</v>
+        <v>406651</v>
       </c>
       <c r="R19" t="n">
-        <v>6969682.069838855</v>
+        <v>6969985</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2732,21 +2477,11 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2755,11 +2490,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2780,15 +2510,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>79105449</v>
+        <v>79105452</v>
       </c>
       <c r="B20" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2796,21 +2521,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2820,10 +2545,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406533.1707199147</v>
+        <v>406633</v>
       </c>
       <c r="R20" t="n">
-        <v>6969745.850776613</v>
+        <v>6969975</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2853,19 +2578,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2896,50 +2611,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>79105409</v>
+        <v>78598350</v>
       </c>
       <c r="B21" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>N om Åviksberget, Västra, Hjd</t>
+          <t>Ö om Åbergstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406633.6254061697</v>
+        <v>406782</v>
       </c>
       <c r="R21" t="n">
-        <v>6969769.950999686</v>
+        <v>6969869</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,22 +2679,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2990,59 +2693,51 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>79105365</v>
+        <v>79105416</v>
       </c>
       <c r="B22" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3052,10 +2747,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>406645.1872898949</v>
+        <v>406686</v>
       </c>
       <c r="R22" t="n">
-        <v>6969983.036775054</v>
+        <v>6969682</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3085,21 +2780,11 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3108,6 +2793,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3128,15 +2818,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>79104083</v>
+        <v>78598364</v>
       </c>
       <c r="B23" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3144,34 +2829,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>N om Åviksberget, Västra, Hjd</t>
+          <t>Ö om Åbergstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>406694.1969218442</v>
+        <v>406782</v>
       </c>
       <c r="R23" t="n">
-        <v>6969663.112870101</v>
+        <v>6969869</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3198,22 +2886,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3222,42 +2900,29 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Asp med bohål</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>79105452</v>
+        <v>79105448</v>
       </c>
       <c r="B24" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3265,21 +2930,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3289,10 +2954,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>406632.6074520887</v>
+        <v>406539</v>
       </c>
       <c r="R24" t="n">
-        <v>6969975.169564396</v>
+        <v>6969918</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3322,19 +2987,14 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>bo, ungar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3365,15 +3025,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>79105357</v>
+        <v>81987619</v>
       </c>
       <c r="B25" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,34 +3036,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221725</v>
+        <v>100077</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>N om Åviksberget, Västra, Hjd</t>
+          <t>södra bäcken, Beten, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>406743.0166012296</v>
+        <v>406429</v>
       </c>
       <c r="R25" t="n">
-        <v>6969866.91927859</v>
+        <v>6969654</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3435,22 +3102,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3465,69 +3122,69 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Kent Moén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kent Moén, Eva Moén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>79105432</v>
+        <v>129939349</v>
       </c>
       <c r="B26" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>100077</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>N om Åviksberget, Västra, Hjd</t>
+          <t>södra bäcken, södra bäcken, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>406573.1510635308</v>
+        <v>406420</v>
       </c>
       <c r="R26" t="n">
-        <v>6969735.570616188</v>
+        <v>6969662</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3551,22 +3208,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3575,38 +3232,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Kent Moén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kent Moén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>79105367</v>
+        <v>79105368</v>
       </c>
       <c r="B27" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3614,21 +3261,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3638,10 +3285,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>406616.0963194038</v>
+        <v>406834</v>
       </c>
       <c r="R27" t="n">
-        <v>6969957.81782157</v>
+        <v>6969638</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3671,19 +3318,14 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3714,15 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>79104090</v>
+        <v>79105419</v>
       </c>
       <c r="B28" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3730,21 +3367,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3754,10 +3391,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>406589.1332638814</v>
+        <v>406697</v>
       </c>
       <c r="R28" t="n">
-        <v>6969943.048875043</v>
+        <v>6969722</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3787,19 +3424,14 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3810,11 +3442,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Låga</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3835,15 +3462,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>79105415</v>
+        <v>79105421</v>
       </c>
       <c r="B29" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3851,21 +3473,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3875,10 +3497,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>406681.0394752442</v>
+        <v>406662</v>
       </c>
       <c r="R29" t="n">
-        <v>6969667.143634233</v>
+        <v>6969771</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3908,19 +3530,14 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3951,37 +3568,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>79105358</v>
+        <v>79105422</v>
       </c>
       <c r="B30" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3991,10 +3603,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>406717.9132676768</v>
+        <v>406652</v>
       </c>
       <c r="R30" t="n">
-        <v>6969997.873931818</v>
+        <v>6969770</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4024,19 +3636,14 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4067,37 +3674,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>79105440</v>
+        <v>79105423</v>
       </c>
       <c r="B31" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4107,10 +3709,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>406655.7299884685</v>
+        <v>406650</v>
       </c>
       <c r="R31" t="n">
-        <v>6969983.650416532</v>
+        <v>6969775</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4140,19 +3742,14 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>spår</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4183,15 +3780,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>79105445</v>
+        <v>79105433</v>
       </c>
       <c r="B32" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4199,21 +3791,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4223,10 +3815,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>406616.2394440522</v>
+        <v>406544</v>
       </c>
       <c r="R32" t="n">
-        <v>6969962.840526664</v>
+        <v>6969730</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4256,19 +3848,14 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>spår</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4299,15 +3886,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>79105454</v>
+        <v>79105434</v>
       </c>
       <c r="B33" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4315,21 +3897,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4339,10 +3921,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>406893.4400264586</v>
+        <v>406547</v>
       </c>
       <c r="R33" t="n">
-        <v>6969749.306498847</v>
+        <v>6969724</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4372,19 +3954,14 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>spår</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4393,7 +3970,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4416,15 +3992,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>79105362</v>
+        <v>79105435</v>
       </c>
       <c r="B34" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4432,21 +4003,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4456,10 +4027,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>406651.1315041334</v>
+        <v>406541</v>
       </c>
       <c r="R34" t="n">
-        <v>6969982.867448056</v>
+        <v>6969715</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4489,19 +4060,14 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>spår</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4532,15 +4098,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>79105430</v>
+        <v>79105436</v>
       </c>
       <c r="B35" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4548,21 +4109,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4572,10 +4133,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>406599.5284534951</v>
+        <v>406540</v>
       </c>
       <c r="R35" t="n">
-        <v>6969745.787067717</v>
+        <v>6969715</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4605,19 +4166,14 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>spår</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4648,15 +4204,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>79105366</v>
+        <v>122073111</v>
       </c>
       <c r="B36" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4664,34 +4215,48 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>N om Åviksberget, Västra, Hjd</t>
+          <t>Storsjö, Beten, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>406634.1506060475</v>
+        <v>406778</v>
       </c>
       <c r="R36" t="n">
-        <v>6969643.799806148</v>
+        <v>6969971</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4718,22 +4283,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4744,40 +4309,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>silverlåga</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Kent Moén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kent Moén, Eva Moén</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>79105369</v>
+        <v>79105410</v>
       </c>
       <c r="B37" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4785,21 +4336,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222412</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4809,10 +4360,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>406722.8320337031</v>
+        <v>406450</v>
       </c>
       <c r="R37" t="n">
-        <v>6969865.208746891</v>
+        <v>6969692</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4842,19 +4393,14 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4885,37 +4431,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>79105448</v>
+        <v>79105437</v>
       </c>
       <c r="B38" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100001</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4925,10 +4466,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>406538.5504503566</v>
+        <v>406530</v>
       </c>
       <c r="R38" t="n">
-        <v>6969918.442911297</v>
+        <v>6969700</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4958,24 +4499,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>bo, ungar</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5006,50 +4532,57 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>79104079</v>
+        <v>131697025</v>
       </c>
       <c r="B39" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57807</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>102622</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N om Åviksberget, Västra, Hjd</t>
+          <t>södra bäcken, Beten, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>406709.1057811959</v>
+        <v>406429</v>
       </c>
       <c r="R39" t="n">
-        <v>6969833.152814791</v>
+        <v>6969654</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5076,22 +4609,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5106,66 +4639,66 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Kent Moén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kent Moén, Eva Moén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>79105424</v>
+        <v>127823971</v>
       </c>
       <c r="B40" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58449</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>102993</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Svart rödstjärt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phoenicurus ochruros</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(S.G. Gmelin, 1774)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N om Åviksberget, Västra, Hjd</t>
+          <t>södra bäcken, Beten, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>406619.1877042255</v>
+        <v>406429</v>
       </c>
       <c r="R40" t="n">
-        <v>6969777.217427101</v>
+        <v>6969654</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5192,22 +4725,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5222,53 +4745,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Kent Moén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kent Moén</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>79105451</v>
+        <v>79105442</v>
       </c>
       <c r="B41" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5278,10 +4792,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>406632.6074520887</v>
+        <v>406648</v>
       </c>
       <c r="R41" t="n">
-        <v>6969975.169564396</v>
+        <v>6969989</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5311,19 +4825,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5354,15 +4858,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>79105412</v>
+        <v>79105445</v>
       </c>
       <c r="B42" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5370,21 +4869,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5394,10 +4893,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>406694.6740933755</v>
+        <v>406616</v>
       </c>
       <c r="R42" t="n">
-        <v>6969615.568773023</v>
+        <v>6969963</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5427,19 +4926,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5470,15 +4959,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>79104082</v>
+        <v>79104092</v>
       </c>
       <c r="B43" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5486,21 +4970,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220093</v>
+        <v>219811</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5510,10 +4994,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>406481.1600792363</v>
+        <v>406483</v>
       </c>
       <c r="R43" t="n">
-        <v>6969895.859709716</v>
+        <v>6969897</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5543,19 +5027,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5586,37 +5060,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>79105418</v>
+        <v>79104082</v>
       </c>
       <c r="B44" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>220093</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5626,10 +5095,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>406666.427867797</v>
+        <v>406481</v>
       </c>
       <c r="R44" t="n">
-        <v>6969700.465007556</v>
+        <v>6969896</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5659,19 +5128,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5702,15 +5161,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>79105414</v>
+        <v>79105438</v>
       </c>
       <c r="B45" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5718,21 +5172,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5742,10 +5196,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>406687.4415533136</v>
+        <v>406467</v>
       </c>
       <c r="R45" t="n">
-        <v>6969666.96135719</v>
+        <v>6969882</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5775,19 +5229,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5818,37 +5262,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>79105413</v>
+        <v>79104085</v>
       </c>
       <c r="B46" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5858,10 +5297,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>406697.8988701853</v>
+        <v>406716</v>
       </c>
       <c r="R46" t="n">
-        <v>6969632.386944307</v>
+        <v>6969980</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5891,19 +5330,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5934,15 +5363,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>79104077</v>
+        <v>79104091</v>
       </c>
       <c r="B47" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5950,21 +5374,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>221343</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5974,10 +5398,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>406640.8557812194</v>
+        <v>406452</v>
       </c>
       <c r="R47" t="n">
-        <v>6969830.9833357</v>
+        <v>6969877</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6007,19 +5431,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6050,50 +5464,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>79105425</v>
+        <v>78598445</v>
       </c>
       <c r="B48" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1467</v>
+        <v>221725</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>N om Åviksberget, Västra, Hjd</t>
+          <t>Ö om Åbergstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>406650.4125382028</v>
+        <v>406772</v>
       </c>
       <c r="R48" t="n">
-        <v>6969780.897951618</v>
+        <v>6969791</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6120,22 +5533,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6144,59 +5547,51 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>79105453</v>
+        <v>79105356</v>
       </c>
       <c r="B49" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>221725</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6206,10 +5601,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>406533.7796297662</v>
+        <v>406912</v>
       </c>
       <c r="R49" t="n">
-        <v>6969943.713153591</v>
+        <v>6969771</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6239,19 +5634,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6282,37 +5667,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>79105441</v>
+        <v>79105357</v>
       </c>
       <c r="B50" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>221725</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6322,10 +5702,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>406650.7392895962</v>
+        <v>406743</v>
       </c>
       <c r="R50" t="n">
-        <v>6969985.163503961</v>
+        <v>6969867</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6355,19 +5735,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6398,15 +5768,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>79105417</v>
+        <v>79105358</v>
       </c>
       <c r="B51" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6414,21 +5779,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229497</v>
+        <v>221725</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6438,10 +5803,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>406683.7289826229</v>
+        <v>406718</v>
       </c>
       <c r="R51" t="n">
-        <v>6969681.234660542</v>
+        <v>6969998</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6471,21 +5836,11 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6494,11 +5849,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6519,15 +5869,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>79104092</v>
+        <v>79105444</v>
       </c>
       <c r="B52" t="n">
-        <v>96336</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6535,21 +5880,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219811</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6559,10 +5904,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>406483.0282070097</v>
+        <v>406626</v>
       </c>
       <c r="R52" t="n">
-        <v>6969897.177372457</v>
+        <v>6969967</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6592,19 +5937,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6638,12 +5973,7 @@
         <v>79105447</v>
       </c>
       <c r="B53" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6675,10 +6005,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>406579.973511189</v>
+        <v>406580</v>
       </c>
       <c r="R53" t="n">
-        <v>6969958.847359221</v>
+        <v>6969959</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6708,19 +6038,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6751,15 +6071,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>79105444</v>
+        <v>79104079</v>
       </c>
       <c r="B54" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6767,16 +6082,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6791,10 +6106,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>406626.4290454874</v>
+        <v>406709</v>
       </c>
       <c r="R54" t="n">
-        <v>6969967.119980373</v>
+        <v>6969833</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6824,19 +6139,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6867,55 +6172,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>79483702</v>
+        <v>79104074</v>
       </c>
       <c r="B55" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Norr Åviksberget, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406651.9424989646</v>
+        <v>406743</v>
       </c>
       <c r="R55" t="n">
-        <v>6969770.343244345</v>
+        <v>6969867</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6945,19 +6240,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6972,67 +6257,61 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Ingemar Södergren</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>79483703</v>
+        <v>79105414</v>
       </c>
       <c r="B56" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Norr Åviksberget, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406650.2304488845</v>
+        <v>406687</v>
       </c>
       <c r="R56" t="n">
-        <v>6969774.505063089</v>
+        <v>6969667</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7062,19 +6341,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7089,67 +6358,61 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Ingemar Södergren</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>79483701</v>
+        <v>79105424</v>
       </c>
       <c r="B57" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Norr Åviksberget, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406662.4988823257</v>
+        <v>406619</v>
       </c>
       <c r="R57" t="n">
-        <v>6969771.413607499</v>
+        <v>6969777</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7179,19 +6442,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7206,67 +6459,61 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Ingemar Södergren</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>79483663</v>
+        <v>79105440</v>
       </c>
       <c r="B58" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Norr Åviksberget, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406540.5423448945</v>
+        <v>406656</v>
       </c>
       <c r="R58" t="n">
-        <v>6969715.477706877</v>
+        <v>6969984</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7296,19 +6543,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7323,67 +6560,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Ingemar Södergren</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>79483661</v>
+        <v>78598369</v>
       </c>
       <c r="B59" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Norr Åviksberget, Hjd</t>
+          <t>Ö om Åbergstjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406543.7027316461</v>
+        <v>406782</v>
       </c>
       <c r="R59" t="n">
-        <v>6969730.012033386</v>
+        <v>6969869</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7410,22 +6645,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7434,55 +6659,51 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Ingemar Södergren</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>79105368</v>
+        <v>79105369</v>
       </c>
       <c r="B60" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>222412</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7492,10 +6713,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406833.9884686128</v>
+        <v>406723</v>
       </c>
       <c r="R60" t="n">
-        <v>6969638.113208781</v>
+        <v>6969865</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7525,24 +6746,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7573,15 +6779,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>79105419</v>
+        <v>79424340</v>
       </c>
       <c r="B61" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7589,21 +6790,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7613,10 +6814,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406697.2327805863</v>
+        <v>406963</v>
       </c>
       <c r="R61" t="n">
-        <v>6969721.524594567</v>
+        <v>6969741</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7646,26 +6847,11 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7674,6 +6860,11 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>granbark</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7683,7 +6874,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7694,15 +6885,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>79105434</v>
+        <v>79105453</v>
       </c>
       <c r="B62" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7710,21 +6896,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7734,10 +6920,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406547.1787033188</v>
+        <v>406534</v>
       </c>
       <c r="R62" t="n">
-        <v>6969723.514730502</v>
+        <v>6969944</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7767,24 +6953,9 @@
           <t>2019-07-24</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2019-07-24</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>spår</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7815,62 +6986,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>81987619</v>
+        <v>79104083</v>
       </c>
       <c r="B63" t="n">
-        <v>57435</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100077</v>
+        <v>229497</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>södra bäcken, Beten, Storsjö, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406429.4000986402</v>
+        <v>406694</v>
       </c>
       <c r="R63" t="n">
-        <v>6969653.752070095</v>
+        <v>6969663</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7897,22 +7051,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2020-02-01</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7923,75 +7067,70 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Asp med bohål</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kent Moén, Eva Moén</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122073111</v>
+        <v>79105417</v>
       </c>
       <c r="B64" t="n">
-        <v>57379</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>229497</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Storsjö, Beten, Storsjö, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406778</v>
+        <v>406684</v>
       </c>
       <c r="R64" t="n">
-        <v>6969971</v>
+        <v>6969681</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8018,22 +7157,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8044,26 +7173,35 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kent Moén, Eva Moén</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127823971</v>
+        <v>79105365</v>
       </c>
       <c r="B65" t="n">
-        <v>58377</v>
+        <v>79917</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8071,43 +7209,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102993</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart rödstjärt</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phoenicurus ochruros</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.G. Gmelin, 1774)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>södra bäcken, Beten, Storsjö, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>406429</v>
+        <v>406645</v>
       </c>
       <c r="R65" t="n">
-        <v>6969654</v>
+        <v>6969983</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8134,12 +7263,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8154,69 +7283,61 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131697025</v>
+        <v>79105366</v>
       </c>
       <c r="B66" t="n">
-        <v>57780</v>
+        <v>79917</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102622</v>
+        <v>229821</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>södra bäcken, Beten, Storsjö, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>406429</v>
+        <v>406634</v>
       </c>
       <c r="R66" t="n">
-        <v>6969654</v>
+        <v>6969644</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8243,22 +7364,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2019-07-24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8269,19 +7380,736 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>silverlåga</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kent Moén, Eva Moén</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>79105367</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>N om Åviksberget, Västra, Hjd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>406616</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6969958</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>79105418</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>N om Åviksberget, Västra, Hjd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>406666</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6969700</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>79105443</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>N om Åviksberget, Västra, Hjd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>406638</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6969980</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>79105460</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>N om Åviksberget, Västra, Hjd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>406492</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6969896</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>79483653</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Norr Åviksberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>406491</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6969896</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>79105370</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>N om Åviksberget, Västra, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>406769</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6969705</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>79424338</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>N om Åviksberget, Västra, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>406604</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6969751</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2019-07-24</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
